--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260629.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260629.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>16,973,000</t>
+          <t>9,865,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>18,944,000</t>
+          <t>16,973,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,865,000</t>
+          <t>18,944,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2,875,000</t>
+          <t>7,878,597</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,878,597</t>
+          <t>2,875,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>10,263,000</t>
+          <t>3,785,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,195,000</t>
+          <t>10,263,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,785,000</t>
+          <t>4,195,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
